--- a/experiment/HAT+CNN_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/HAT+CNN_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.03</v>
+        <v>23.04</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5349</v>
+        <v>0.5351</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.32</v>
+        <v>26.28</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7595</v>
+        <v>0.7585</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>25.36</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6349</v>
+        <v>0.6351</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>26.29</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5779</v>
+        <v>0.5773</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>23.56</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7389</v>
+        <v>0.7391</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>32.93</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7958</v>
+        <v>0.7957</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.37</v>
+        <v>28.36</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8222</v>
+        <v>0.822</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.57</v>
+        <v>33.63</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9171</v>
+        <v>0.9177999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8661</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="11">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.32</v>
+        <v>27.31</v>
       </c>
       <c r="C11" t="n">
         <v>0.7492</v>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33.01</v>
+        <v>33.02</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9452</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.37</v>
+        <v>34.34</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8813</v>
+        <v>0.8812</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.78</v>
+        <v>26.76</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9515</v>
+        <v>0.9513</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.47</v>
+        <v>27.48</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7794</v>
+        <v>0.7796</v>
       </c>
     </row>
     <row r="16">
